--- a/Result/profitability/3057.xlsx
+++ b/Result/profitability/3057.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.27</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.23625</v>
+        <v>-0.24375</v>
       </c>
       <c r="N2" t="n">
-        <v>37.15</v>
+        <v>38.51625</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.61</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.11</v>
+        <v>-0.065</v>
       </c>
       <c r="N3" t="n">
-        <v>39.90375</v>
+        <v>40.92875</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.72</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0825</v>
+        <v>-0.08249999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>42.65375</v>
+        <v>43.86875</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -911,7 +911,7 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
@@ -920,7 +920,7 @@
         <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -1018,16 +1018,16 @@
         <v>-0.39</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.07375</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>43.575</v>
+        <v>45.1825</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.26</v>
       </c>
       <c r="M6" t="n">
-        <v>0.05</v>
+        <v>0.04749999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>45.9125</v>
+        <v>46.10625</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.15</v>
       </c>
       <c r="M7" t="n">
-        <v>0.12375</v>
+        <v>0.1475</v>
       </c>
       <c r="N7" t="n">
-        <v>46.8875</v>
+        <v>48.57875</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.37</v>
       </c>
       <c r="M8" t="n">
-        <v>0.25125</v>
+        <v>0.19125</v>
       </c>
       <c r="N8" t="n">
-        <v>49.49625</v>
+        <v>49.23</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -2029,7 +2029,7 @@
         <v>0.14</v>
       </c>
       <c r="N13" t="n">
-        <v>50.16249999999999</v>
+        <v>50.1625</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3057</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>125</v>
+      </c>
+      <c r="D75" t="n">
+        <v>71</v>
+      </c>
+      <c r="E75" t="n">
+        <v>54</v>
+      </c>
+      <c r="F75" t="n">
+        <v>42.95</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-28</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-22.47%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-3</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-31</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-31</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.46</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.3275</v>
+      </c>
+      <c r="N75" t="n">
+        <v>36.1175</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.48</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-24</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-2.129999999999995</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.04724933451641511</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.3698630136986301</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>12.86</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.4273845131272849</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
